--- a/#game_anonymized.xlsx
+++ b/#game_anonymized.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12292,7 +12292,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13012,7 +13012,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13400,7 +13400,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13489,7 +13489,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13667,7 +13667,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14136,7 +14136,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14676,7 +14676,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14844,7 +14844,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15324,7 +15324,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15504,7 +15504,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15549,7 +15549,7 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15865,7 +15865,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16653,7 +16653,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16695,7 +16695,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16821,7 +16821,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16911,7 +16911,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17037,7 +17037,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17771,7 +17771,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17860,7 +17860,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17903,7 +17903,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17946,7 +17946,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18120,7 +18120,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18162,7 +18162,7 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18208,7 +18208,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18300,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18438,7 +18438,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18576,7 +18576,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18749,7 +18749,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18834,7 +18834,7 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18919,7 +18919,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19136,7 +19136,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19316,7 +19316,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19460,7 +19460,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19687,7 +19687,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19942,7 +19942,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20156,7 +20156,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20368,7 +20368,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20415,7 +20415,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20558,7 +20558,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20696,7 +20696,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20745,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21141,7 +21141,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21312,7 +21312,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21516,7 +21516,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21555,7 +21555,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21633,7 +21633,7 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21711,7 +21711,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21912,7 +21912,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22033,7 +22033,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22073,7 +22073,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22113,7 +22113,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22195,7 +22195,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22233,7 +22233,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22271,7 +22271,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22347,7 +22347,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22385,7 +22385,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22461,7 +22461,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22618,7 +22618,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22695,7 +22695,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22809,7 +22809,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22847,7 +22847,7 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22885,7 +22885,7 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22923,7 +22923,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22961,7 +22961,7 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23004,7 +23004,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23092,7 +23092,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23176,7 +23176,7 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23218,7 +23218,7 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23387,7 +23387,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23425,7 +23425,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23660,7 +23660,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23738,7 +23738,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23936,7 +23936,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23979,7 +23979,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24023,7 +24023,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24158,7 +24158,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24203,7 +24203,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24246,7 +24246,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24288,7 +24288,7 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24330,7 +24330,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24375,7 +24375,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24463,7 +24463,7 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24508,7 +24508,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24592,7 +24592,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24636,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24679,7 +24679,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24768,7 +24768,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24860,7 +24860,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24906,7 +24906,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25133,7 +25133,7 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25172,7 +25172,7 @@
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25212,7 +25212,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25251,7 +25251,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25290,7 +25290,7 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25329,7 +25329,7 @@
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25368,7 +25368,7 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25451,7 +25451,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25490,7 +25490,7 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25529,7 +25529,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25619,7 +25619,7 @@
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25663,7 +25663,7 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25709,7 +25709,7 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25756,7 +25756,7 @@
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25853,7 +25853,7 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25997,7 +25997,7 @@
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26176,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26219,7 +26219,7 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26263,7 +26263,7 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26305,7 +26305,7 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26434,7 +26434,7 @@
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26653,7 +26653,7 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26791,7 +26791,7 @@
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26837,7 +26837,7 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26883,7 +26883,7 @@
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26976,7 +26976,7 @@
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27023,7 +27023,7 @@
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27065,7 +27065,7 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27107,7 +27107,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27196,7 +27196,7 @@
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27238,7 +27238,7 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27280,7 +27280,7 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27364,7 +27364,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27448,7 +27448,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27490,7 +27490,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27538,7 +27538,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27583,7 +27583,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27627,7 +27627,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27672,7 +27672,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27758,7 +27758,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27934,7 +27934,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28064,7 +28064,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28150,7 +28150,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28194,7 +28194,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28237,7 +28237,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28280,7 +28280,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28324,7 +28324,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28367,7 +28367,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28531,7 +28531,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28572,7 +28572,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28613,7 +28613,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28695,7 +28695,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28736,7 +28736,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28822,7 +28822,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28866,7 +28866,7 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28954,7 +28954,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28997,7 +28997,7 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29039,7 +29039,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29085,7 +29085,7 @@
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29266,7 +29266,7 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29308,7 +29308,7 @@
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29350,7 +29350,7 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29392,7 +29392,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29476,7 +29476,7 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29518,7 +29518,7 @@
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29560,7 +29560,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29602,7 +29602,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29644,7 +29644,7 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29724,7 +29724,7 @@
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29762,7 +29762,7 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29800,7 +29800,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29876,7 +29876,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29914,7 +29914,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29952,7 +29952,7 @@
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30028,7 +30028,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30123,7 +30123,7 @@
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30170,7 +30170,7 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30217,7 +30217,7 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30264,7 +30264,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30452,7 +30452,7 @@
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30542,7 +30542,7 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30671,7 +30671,7 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30714,7 +30714,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30757,7 +30757,7 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30800,7 +30800,7 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30886,7 +30886,7 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30971,7 +30971,7 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31055,7 +31055,7 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31097,7 +31097,7 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31187,7 +31187,7 @@
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31229,7 +31229,7 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31271,7 +31271,7 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31313,7 +31313,7 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31355,7 +31355,7 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31398,7 +31398,7 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31443,7 +31443,7 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31488,7 +31488,7 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31535,7 +31535,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31581,7 +31581,7 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31629,7 +31629,7 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31671,7 +31671,7 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31714,7 +31714,7 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31758,7 +31758,7 @@
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31805,7 +31805,7 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31850,7 +31850,7 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31937,7 +31937,7 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32029,7 +32029,7 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32121,7 +32121,7 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32166,7 +32166,7 @@
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32210,7 +32210,7 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32299,7 +32299,7 @@
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32384,7 +32384,7 @@
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32428,7 +32428,7 @@
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32472,7 +32472,7 @@
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32557,7 +32557,7 @@
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32599,7 +32599,7 @@
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32644,7 +32644,7 @@
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32689,7 +32689,7 @@
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32733,7 +32733,7 @@
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32782,7 +32782,7 @@
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32825,7 +32825,7 @@
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32920,7 +32920,7 @@
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32968,7 +32968,7 @@
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33019,7 +33019,7 @@
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33067,7 +33067,7 @@
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33201,7 +33201,7 @@
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33244,7 +33244,7 @@
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33287,7 +33287,7 @@
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33335,7 +33335,7 @@
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33380,7 +33380,7 @@
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33466,7 +33466,7 @@
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33509,7 +33509,7 @@
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33552,7 +33552,7 @@
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33595,7 +33595,7 @@
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33643,7 +33643,7 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33685,7 +33685,7 @@
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33728,7 +33728,7 @@
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33771,7 +33771,7 @@
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33856,7 +33856,7 @@
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33899,7 +33899,7 @@
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33941,7 +33941,7 @@
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33985,7 +33985,7 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34027,7 +34027,7 @@
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34069,7 +34069,7 @@
       </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34153,7 +34153,7 @@
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34195,7 +34195,7 @@
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34280,7 +34280,7 @@
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34322,7 +34322,7 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34364,7 +34364,7 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34448,7 +34448,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34490,7 +34490,7 @@
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34532,7 +34532,7 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34576,7 +34576,7 @@
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34618,7 +34618,7 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34660,7 +34660,7 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34704,7 +34704,7 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34750,7 +34750,7 @@
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34879,7 +34879,7 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34966,7 +34966,7 @@
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35008,7 +35008,7 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35051,7 +35051,7 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35094,7 +35094,7 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35136,7 +35136,7 @@
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35179,7 +35179,7 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35221,7 +35221,7 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35312,7 +35312,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35358,7 +35358,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35402,7 +35402,7 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35445,7 +35445,7 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35489,7 +35489,7 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35533,7 +35533,7 @@
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35576,7 +35576,7 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35619,7 +35619,7 @@
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35663,7 +35663,7 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35805,7 +35805,7 @@
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35847,7 +35847,7 @@
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35934,7 +35934,7 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -35980,7 +35980,7 @@
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36022,7 +36022,7 @@
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36065,7 +36065,7 @@
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36111,7 @@
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36154,7 +36154,7 @@
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36196,7 +36196,7 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36241,7 +36241,7 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36283,7 +36283,7 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36328,7 +36328,7 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36419,7 +36419,7 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36461,7 +36461,7 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36546,7 +36546,7 @@
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36588,7 +36588,7 @@
       </c>
       <c r="J834" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36631,7 +36631,7 @@
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36675,7 +36675,7 @@
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36761,7 +36761,7 @@
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36803,7 +36803,7 @@
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36845,7 +36845,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36887,7 +36887,7 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36931,7 +36931,7 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37017,7 +37017,7 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37059,7 +37059,7 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37103,7 +37103,7 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37148,7 +37148,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37194,7 +37194,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37290,7 +37290,7 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37333,7 +37333,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37375,7 +37375,7 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37461,7 +37461,7 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -37508,7 +37508,7 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
